--- a/data/trans_orig/IP2902-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2902-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28677</t>
+          <t>28978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22793</t>
+          <t>22679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30416</t>
+          <t>29364</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48151</t>
+          <t>46403</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>22944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26586</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28356</t>
+          <t>28279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45677</t>
+          <t>46037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52633</t>
+          <t>52774</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68325</t>
+          <t>67708</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50365</t>
+          <t>50970</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65168</t>
+          <t>66216</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>107743</t>
+          <t>109005</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>129108</t>
+          <t>130662</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,45%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25492</t>
+          <t>25411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>25159</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28732</t>
+          <t>28034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46490</t>
+          <t>46093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27856</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51384</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65811</t>
+          <t>65591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46449</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61168</t>
+          <t>60378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102997</t>
+          <t>101594</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122049</t>
+          <t>121715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21053</t>
+          <t>21503</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27739</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47278</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17456</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16965</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30824</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32052</t>
+          <t>32663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45283</t>
+          <t>45636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54968</t>
+          <t>54360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>69315</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91107</t>
+          <t>91560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111544</t>
+          <t>111093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37776</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56098</t>
+          <t>55720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37939</t>
+          <t>37943</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58021</t>
+          <t>57641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79838</t>
+          <t>79980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106472</t>
+          <t>106876</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19508</t>
+          <t>19207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>33821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>18603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32953</t>
+          <t>34586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41113</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62149</t>
+          <t>62985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111915</t>
+          <t>114090</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133830</t>
+          <t>135176</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>110828</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>130692</t>
+          <t>131983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>229212</t>
+          <t>229925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>260581</t>
+          <t>261666</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23622</t>
+          <t>23821</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34918</t>
+          <t>33501</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51336</t>
+          <t>50372</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62494</t>
+          <t>62527</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84637</t>
+          <t>84348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20851</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27936</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>54734</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71154</t>
+          <t>70916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58156</t>
+          <t>58562</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75394</t>
+          <t>76116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119462</t>
+          <t>118669</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142281</t>
+          <t>142959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12070</t>
+          <t>12486</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23377</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23488</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39338</t>
+          <t>40038</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15457</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48344</t>
+          <t>48911</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60831</t>
+          <t>60855</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40529</t>
+          <t>41580</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53054</t>
+          <t>53629</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>93307</t>
+          <t>93502</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>110884</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,6%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>129858</t>
+          <t>129939</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>164224</t>
+          <t>162160</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>146595</t>
+          <t>146744</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>182742</t>
+          <t>182167</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>285826</t>
+          <t>284742</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>335089</t>
+          <t>332164</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61096</t>
+          <t>60993</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>86383</t>
+          <t>86901</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76063</t>
+          <t>75954</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104878</t>
+          <t>104397</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>143686</t>
+          <t>145206</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>178866</t>
+          <t>182938</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>381254</t>
+          <t>381481</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>418871</t>
+          <t>419276</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>389426</t>
+          <t>388729</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>430558</t>
+          <t>430605</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>782590</t>
+          <t>785179</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>840371</t>
+          <t>838977</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,41%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30190</t>
+          <t>29882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57006</t>
+          <t>57877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22549</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17593</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32801</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>49942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63933</t>
+          <t>64157</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41906</t>
+          <t>42073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56595</t>
+          <t>56746</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>95674</t>
+          <t>95011</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116717</t>
+          <t>118408</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>17876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>31836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23983</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39500</t>
+          <t>39379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44869</t>
+          <t>44880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65168</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15308</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20661</t>
+          <t>21136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32406</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50103</t>
+          <t>49693</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65191</t>
+          <t>65302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41131</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56373</t>
+          <t>56175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96260</t>
+          <t>94787</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118245</t>
+          <t>117586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,35%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>30867</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31203</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39074</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57405</t>
+          <t>58315</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20296</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34247</t>
+          <t>33818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41936</t>
+          <t>42503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56965</t>
+          <t>57121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>38673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54269</t>
+          <t>53898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85523</t>
+          <t>85802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106765</t>
+          <t>106992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,07%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46637</t>
+          <t>46685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68222</t>
+          <t>69087</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58271</t>
+          <t>58331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81591</t>
+          <t>81983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111919</t>
+          <t>111053</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142708</t>
+          <t>142572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19661</t>
+          <t>20101</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35956</t>
+          <t>36061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>12386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26222</t>
+          <t>25961</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>36086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57674</t>
+          <t>56577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107982</t>
+          <t>106911</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130450</t>
+          <t>131034</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>123437</t>
+          <t>123148</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>147761</t>
+          <t>148252</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>238744</t>
+          <t>238130</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>270924</t>
+          <t>272287</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56375</t>
+          <t>57184</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>40261</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59138</t>
+          <t>59767</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85116</t>
+          <t>84058</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110704</t>
+          <t>110834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>19274</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20332</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19250</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>35825</t>
+          <t>35792</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76949</t>
+          <t>77479</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97497</t>
+          <t>96663</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65616</t>
+          <t>65836</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85611</t>
+          <t>85478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>149451</t>
+          <t>149617</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177789</t>
+          <t>176894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,62%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28083</t>
+          <t>27915</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>27672</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44649</t>
+          <t>44558</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18799</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30113</t>
+          <t>30434</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>23723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35340</t>
+          <t>35568</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43650</t>
+          <t>44240</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>57875</t>
+          <t>57098</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>75633</t>
+          <t>74738</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>59,9%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>170236</t>
+          <t>170423</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>210698</t>
+          <t>208671</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>200943</t>
+          <t>198442</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>241265</t>
+          <t>242038</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>381947</t>
+          <t>381724</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>437424</t>
+          <t>435163</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>66828</t>
+          <t>66549</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>94178</t>
+          <t>94311</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74988</t>
+          <t>75834</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>103381</t>
+          <t>104751</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>149184</t>
+          <t>151095</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>188969</t>
+          <t>188639</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>377872</t>
+          <t>381188</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>419890</t>
+          <t>421488</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>370981</t>
+          <t>370627</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>415524</t>
+          <t>415296</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>763901</t>
+          <t>766452</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>820548</t>
+          <t>826378</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>18153</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>19013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33240</t>
+          <t>32920</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>13199</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>25750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25384</t>
+          <t>24445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40672</t>
+          <t>41293</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50543</t>
+          <t>49888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63846</t>
+          <t>63790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55222</t>
+          <t>55300</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69827</t>
+          <t>70559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>110981</t>
+          <t>110457</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>130507</t>
+          <t>130995</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,78%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29597</t>
+          <t>29466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24444</t>
+          <t>23521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>30820</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48550</t>
+          <t>49541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>21981</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15347</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29230</t>
+          <t>29523</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>28136</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47121</t>
+          <t>47470</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58134</t>
+          <t>58044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73797</t>
+          <t>73783</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>61465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77933</t>
+          <t>78751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126292</t>
+          <t>123245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148326</t>
+          <t>147966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20164</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>33938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21045</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34600</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31064</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38321</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51693</t>
+          <t>51386</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73546</t>
+          <t>73266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91346</t>
+          <t>91159</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34966</t>
+          <t>34685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54524</t>
+          <t>54222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>35580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54377</t>
+          <t>54871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74338</t>
+          <t>75674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101345</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28020</t>
+          <t>27564</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45768</t>
+          <t>44672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,47 +9080,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>26247</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19266</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>34241</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>12,9%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26247</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19126</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>35226</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51013</t>
+          <t>51583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75246</t>
+          <t>75061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125039</t>
+          <t>125790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>147102</t>
+          <t>148842</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>121042</t>
+          <t>122695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>143835</t>
+          <t>143569</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>254219</t>
+          <t>255239</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>285581</t>
+          <t>285974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20514</t>
+          <t>21465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36599</t>
+          <t>36182</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34603</t>
+          <t>35096</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>45067</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65772</t>
+          <t>66799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>28188</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27278</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31753</t>
+          <t>32145</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>51057</t>
+          <t>51515</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72446</t>
+          <t>73196</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90818</t>
+          <t>90764</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84354</t>
+          <t>83278</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101850</t>
+          <t>102221</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>162405</t>
+          <t>161048</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>187521</t>
+          <t>188036</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20831</t>
+          <t>20601</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36317</t>
+          <t>36092</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35452</t>
+          <t>35213</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>47088</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50973</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>78155</t>
+          <t>78656</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95702</t>
+          <t>95801</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>116552</t>
+          <t>116087</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>149076</t>
+          <t>148987</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>114147</t>
+          <t>112836</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>148199</t>
+          <t>146031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>237318</t>
+          <t>237644</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>283534</t>
+          <t>283405</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87730</t>
+          <t>88368</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116703</t>
+          <t>118751</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>96495</t>
+          <t>95567</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>129345</t>
+          <t>126924</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>192270</t>
+          <t>191313</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>235624</t>
+          <t>233548</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>403039</t>
+          <t>402256</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>441920</t>
+          <t>440736</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>428887</t>
+          <t>428815</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>469383</t>
+          <t>471150</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>845165</t>
+          <t>845756</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>901890</t>
+          <t>901664</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
